--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -1313,7 +1313,7 @@
         <v>132318246</v>
       </c>
       <c r="B8" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>132318248</v>
       </c>
       <c r="B9" t="n">
-        <v>97963</v>
+        <v>97966</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>132318247</v>
       </c>
       <c r="B10" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -1313,7 +1313,7 @@
         <v>132318246</v>
       </c>
       <c r="B8" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>132318248</v>
       </c>
       <c r="B9" t="n">
-        <v>97966</v>
+        <v>97974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>132318247</v>
       </c>
       <c r="B10" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -1313,7 +1313,7 @@
         <v>132318246</v>
       </c>
       <c r="B8" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>132318248</v>
       </c>
       <c r="B9" t="n">
-        <v>97974</v>
+        <v>97984</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>132318247</v>
       </c>
       <c r="B10" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -1419,7 +1419,7 @@
         <v>132318248</v>
       </c>
       <c r="B9" t="n">
-        <v>97984</v>
+        <v>97985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>132318247</v>
       </c>
       <c r="B10" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -1419,7 +1419,7 @@
         <v>132318248</v>
       </c>
       <c r="B9" t="n">
-        <v>97985</v>
+        <v>97986</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -1313,7 +1313,7 @@
         <v>132318246</v>
       </c>
       <c r="B8" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>132318248</v>
       </c>
       <c r="B9" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>132318247</v>
       </c>
       <c r="B10" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133163899</v>
+        <v>133164017</v>
       </c>
       <c r="B21" t="n">
-        <v>5178</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102204</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478815</v>
+        <v>478847</v>
       </c>
       <c r="R21" t="n">
-        <v>6587811</v>
+        <v>6587896</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133164017</v>
+        <v>133163899</v>
       </c>
       <c r="B23" t="n">
-        <v>79333</v>
+        <v>5178</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>102204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478847</v>
+        <v>478815</v>
       </c>
       <c r="R23" t="n">
-        <v>6587896</v>
+        <v>6587811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -5501,7 +5501,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133328970</v>
+        <v>133328895</v>
       </c>
       <c r="B45" t="n">
         <v>58119</v>
@@ -5539,23 +5539,21 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478780</v>
+        <v>478749</v>
       </c>
       <c r="R45" t="n">
-        <v>6587952</v>
+        <v>6587791</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5587,7 +5585,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>05:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5597,12 +5595,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>05:33</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Filmsnutt finns sparad.</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5629,7 +5627,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133328895</v>
+        <v>133328970</v>
       </c>
       <c r="B46" t="n">
         <v>58119</v>
@@ -5667,21 +5665,23 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478749</v>
+        <v>478780</v>
       </c>
       <c r="R46" t="n">
-        <v>6587791</v>
+        <v>6587952</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>05:33</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>05:33</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Spel/sång.</t>
+          <t>Filmsnutt finns sparad.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133157943</v>
+        <v>133163899</v>
       </c>
       <c r="B22" t="n">
-        <v>79923</v>
+        <v>5178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>102204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478785</v>
+        <v>478815</v>
       </c>
       <c r="R22" t="n">
-        <v>6587651</v>
+        <v>6587811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133163899</v>
+        <v>133157943</v>
       </c>
       <c r="B23" t="n">
-        <v>5178</v>
+        <v>79923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102204</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478815</v>
+        <v>478785</v>
       </c>
       <c r="R23" t="n">
-        <v>6587811</v>
+        <v>6587651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3290,45 +3290,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133158861</v>
+        <v>133159508</v>
       </c>
       <c r="B26" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478760</v>
+        <v>478797</v>
       </c>
       <c r="R26" t="n">
-        <v>6587688</v>
+        <v>6587811</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,7 +3374,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3370,7 +3384,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bohål i tallhögstubbe passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3397,59 +3416,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133159508</v>
+        <v>133158861</v>
       </c>
       <c r="B27" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478797</v>
+        <v>478760</v>
       </c>
       <c r="R27" t="n">
-        <v>6587811</v>
+        <v>6587688</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3481,7 +3486,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3491,12 +3496,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Bohål i tallhögstubbe passande för pärluggla.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133164491</v>
+        <v>133158110</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478853</v>
+        <v>478783</v>
       </c>
       <c r="R35" t="n">
-        <v>6587853</v>
+        <v>6587658</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,32 +4498,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133158110</v>
+        <v>133164491</v>
       </c>
       <c r="B36" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478783</v>
+        <v>478853</v>
       </c>
       <c r="R36" t="n">
-        <v>6587658</v>
+        <v>6587853</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133158110</v>
+        <v>133164491</v>
       </c>
       <c r="B35" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478783</v>
+        <v>478853</v>
       </c>
       <c r="R35" t="n">
-        <v>6587658</v>
+        <v>6587853</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,32 +4498,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133164491</v>
+        <v>133158110</v>
       </c>
       <c r="B36" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478853</v>
+        <v>478783</v>
       </c>
       <c r="R36" t="n">
-        <v>6587853</v>
+        <v>6587658</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -3290,59 +3290,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133159508</v>
+        <v>133158861</v>
       </c>
       <c r="B26" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478797</v>
+        <v>478760</v>
       </c>
       <c r="R26" t="n">
-        <v>6587811</v>
+        <v>6587688</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3374,7 +3360,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3384,12 +3370,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Bohål i tallhögstubbe passande för pärluggla.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3416,10 +3397,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133158861</v>
+        <v>133164945</v>
       </c>
       <c r="B27" t="n">
-        <v>91881</v>
+        <v>57145</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3427,34 +3408,53 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478760</v>
+        <v>478829</v>
       </c>
       <c r="R27" t="n">
-        <v>6587688</v>
+        <v>6587835</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3523,7 +3523,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133164945</v>
+        <v>133159244</v>
       </c>
       <c r="B28" t="n">
         <v>57145</v>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478829</v>
+        <v>478774</v>
       </c>
       <c r="R28" t="n">
-        <v>6587835</v>
+        <v>6587757</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,32 +3649,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133159244</v>
+        <v>133159508</v>
       </c>
       <c r="B29" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3687,14 +3687,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3703,10 +3698,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478774</v>
+        <v>478797</v>
       </c>
       <c r="R29" t="n">
-        <v>6587757</v>
+        <v>6587811</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3738,7 +3733,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3748,7 +3743,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bohål i tallhögstubbe passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3775,45 +3775,64 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133163490</v>
+        <v>133165225</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478839</v>
+        <v>478778</v>
       </c>
       <c r="R30" t="n">
-        <v>6587846</v>
+        <v>6587929</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3845,7 +3864,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3855,7 +3874,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3882,32 +3901,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133165225</v>
+        <v>133157237</v>
       </c>
       <c r="B31" t="n">
-        <v>57145</v>
+        <v>58119</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3920,26 +3939,21 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478778</v>
+        <v>478750</v>
       </c>
       <c r="R31" t="n">
-        <v>6587929</v>
+        <v>6587597</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3971,7 +3985,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3981,7 +3995,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4008,10 +4027,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133157237</v>
+        <v>133163490</v>
       </c>
       <c r="B32" t="n">
-        <v>58119</v>
+        <v>79333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4019,48 +4038,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478750</v>
+        <v>478839</v>
       </c>
       <c r="R32" t="n">
-        <v>6587597</v>
+        <v>6587846</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4092,7 +4097,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4102,12 +4107,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4134,32 +4134,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133163377</v>
+        <v>133157471</v>
       </c>
       <c r="B33" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4172,6 +4172,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4183,10 +4188,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478858</v>
+        <v>478782</v>
       </c>
       <c r="R33" t="n">
-        <v>6587872</v>
+        <v>6587621</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4218,7 +4223,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4228,12 +4233,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Inhack efter hästmyror i innanmurken torrgran.</t>
+          <t>Nyligen använd sandbadgrop med tappat dun.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4260,32 +4265,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133157471</v>
+        <v>133163377</v>
       </c>
       <c r="B34" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4298,11 +4303,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478782</v>
+        <v>478858</v>
       </c>
       <c r="R34" t="n">
-        <v>6587621</v>
+        <v>6587872</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4359,12 +4359,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Nyligen använd sandbadgrop med tappat dun.</t>
+          <t>Inhack efter hästmyror i innanmurken torrgran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133164491</v>
+        <v>133158110</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478853</v>
+        <v>478783</v>
       </c>
       <c r="R35" t="n">
-        <v>6587853</v>
+        <v>6587658</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,32 +4498,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133158110</v>
+        <v>133164491</v>
       </c>
       <c r="B36" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478783</v>
+        <v>478853</v>
       </c>
       <c r="R36" t="n">
-        <v>6587658</v>
+        <v>6587853</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -3775,32 +3775,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133165225</v>
+        <v>133157237</v>
       </c>
       <c r="B30" t="n">
-        <v>57145</v>
+        <v>58119</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3813,26 +3813,21 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478778</v>
+        <v>478750</v>
       </c>
       <c r="R30" t="n">
-        <v>6587929</v>
+        <v>6587597</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3864,7 +3859,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3874,7 +3869,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3901,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133157237</v>
+        <v>133163490</v>
       </c>
       <c r="B31" t="n">
-        <v>58119</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,48 +3912,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478750</v>
+        <v>478839</v>
       </c>
       <c r="R31" t="n">
-        <v>6587597</v>
+        <v>6587846</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3985,7 +3971,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3995,12 +3981,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4027,45 +4008,64 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133163490</v>
+        <v>133165225</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478839</v>
+        <v>478778</v>
       </c>
       <c r="R32" t="n">
-        <v>6587846</v>
+        <v>6587929</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133158110</v>
+        <v>133164491</v>
       </c>
       <c r="B35" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478783</v>
+        <v>478853</v>
       </c>
       <c r="R35" t="n">
-        <v>6587658</v>
+        <v>6587853</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,32 +4498,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133164491</v>
+        <v>133158110</v>
       </c>
       <c r="B36" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478853</v>
+        <v>478783</v>
       </c>
       <c r="R36" t="n">
-        <v>6587853</v>
+        <v>6587658</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133165025</v>
+        <v>133163939</v>
       </c>
       <c r="B13" t="n">
         <v>57145</v>
@@ -1892,14 +1892,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478792</v>
+        <v>478815</v>
       </c>
       <c r="R13" t="n">
-        <v>6587923</v>
+        <v>6587811</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,7 +1968,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133163939</v>
+        <v>133165025</v>
       </c>
       <c r="B14" t="n">
         <v>57145</v>
@@ -2018,14 +2018,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478815</v>
+        <v>478792</v>
       </c>
       <c r="R14" t="n">
-        <v>6587811</v>
+        <v>6587923</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,7 +2094,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133164100</v>
+        <v>133164621</v>
       </c>
       <c r="B15" t="n">
         <v>79333</v>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478836</v>
+        <v>478849</v>
       </c>
       <c r="R15" t="n">
-        <v>6587889</v>
+        <v>6587928</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,7 +2201,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133164621</v>
+        <v>133164100</v>
       </c>
       <c r="B16" t="n">
         <v>79333</v>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478849</v>
+        <v>478836</v>
       </c>
       <c r="R16" t="n">
-        <v>6587928</v>
+        <v>6587889</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133163899</v>
+        <v>133157943</v>
       </c>
       <c r="B22" t="n">
-        <v>5178</v>
+        <v>79923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102204</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478815</v>
+        <v>478785</v>
       </c>
       <c r="R22" t="n">
-        <v>6587811</v>
+        <v>6587651</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133157943</v>
+        <v>133163899</v>
       </c>
       <c r="B23" t="n">
-        <v>79923</v>
+        <v>5178</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>102204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478785</v>
+        <v>478815</v>
       </c>
       <c r="R23" t="n">
-        <v>6587651</v>
+        <v>6587811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4134,32 +4134,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133157471</v>
+        <v>133163377</v>
       </c>
       <c r="B33" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4172,11 +4172,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4188,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478782</v>
+        <v>478858</v>
       </c>
       <c r="R33" t="n">
-        <v>6587621</v>
+        <v>6587872</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4223,7 +4218,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4233,12 +4228,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Nyligen använd sandbadgrop med tappat dun.</t>
+          <t>Inhack efter hästmyror i innanmurken torrgran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4265,32 +4260,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133163377</v>
+        <v>133157471</v>
       </c>
       <c r="B34" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4303,6 +4298,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478858</v>
+        <v>478782</v>
       </c>
       <c r="R34" t="n">
-        <v>6587872</v>
+        <v>6587621</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4359,12 +4359,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Inhack efter hästmyror i innanmurken torrgran.</t>
+          <t>Nyligen använd sandbadgrop med tappat dun.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133164491</v>
+        <v>133158110</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478853</v>
+        <v>478783</v>
       </c>
       <c r="R35" t="n">
-        <v>6587853</v>
+        <v>6587658</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,32 +4498,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133158110</v>
+        <v>133164491</v>
       </c>
       <c r="B36" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478783</v>
+        <v>478853</v>
       </c>
       <c r="R36" t="n">
-        <v>6587658</v>
+        <v>6587853</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -3057,45 +3057,59 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133164424</v>
+        <v>133158095</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478877</v>
+        <v>478787</v>
       </c>
       <c r="R24" t="n">
-        <v>6587894</v>
+        <v>6587663</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,7 +3141,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3137,7 +3151,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Nyligen använd sandbadgrop.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3164,59 +3183,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133158095</v>
+        <v>133164424</v>
       </c>
       <c r="B25" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478787</v>
+        <v>478877</v>
       </c>
       <c r="R25" t="n">
-        <v>6587663</v>
+        <v>6587894</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3248,7 +3253,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3258,12 +3263,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Nyligen använd sandbadgrop.</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3775,32 +3775,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133157237</v>
+        <v>133165225</v>
       </c>
       <c r="B30" t="n">
-        <v>58119</v>
+        <v>57145</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3813,21 +3813,26 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478750</v>
+        <v>478778</v>
       </c>
       <c r="R30" t="n">
-        <v>6587597</v>
+        <v>6587929</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3859,7 +3864,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3869,12 +3874,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3901,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133163490</v>
+        <v>133157237</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>58119</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,34 +3912,48 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478839</v>
+        <v>478750</v>
       </c>
       <c r="R31" t="n">
-        <v>6587846</v>
+        <v>6587597</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3971,7 +3985,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3981,7 +3995,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4008,64 +4027,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133165225</v>
+        <v>133163490</v>
       </c>
       <c r="B32" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478778</v>
+        <v>478839</v>
       </c>
       <c r="R32" t="n">
-        <v>6587929</v>
+        <v>6587846</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133164017</v>
+        <v>133163899</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>5178</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478847</v>
+        <v>478815</v>
       </c>
       <c r="R21" t="n">
-        <v>6587896</v>
+        <v>6587811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133157943</v>
+        <v>133164017</v>
       </c>
       <c r="B22" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478785</v>
+        <v>478847</v>
       </c>
       <c r="R22" t="n">
-        <v>6587651</v>
+        <v>6587896</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133163899</v>
+        <v>133157943</v>
       </c>
       <c r="B23" t="n">
-        <v>5178</v>
+        <v>79923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102204</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478815</v>
+        <v>478785</v>
       </c>
       <c r="R23" t="n">
-        <v>6587811</v>
+        <v>6587651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,59 +3057,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133158095</v>
+        <v>133164424</v>
       </c>
       <c r="B24" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478787</v>
+        <v>478877</v>
       </c>
       <c r="R24" t="n">
-        <v>6587663</v>
+        <v>6587894</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,7 +3127,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3151,12 +3137,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Nyligen använd sandbadgrop.</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3183,45 +3164,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133164424</v>
+        <v>133158095</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478877</v>
+        <v>478787</v>
       </c>
       <c r="R25" t="n">
-        <v>6587894</v>
+        <v>6587663</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,7 +3248,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3263,7 +3258,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Nyligen använd sandbadgrop.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133163899</v>
+        <v>133164017</v>
       </c>
       <c r="B21" t="n">
-        <v>5178</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102204</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478815</v>
+        <v>478847</v>
       </c>
       <c r="R21" t="n">
-        <v>6587811</v>
+        <v>6587896</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133164017</v>
+        <v>133157943</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478847</v>
+        <v>478785</v>
       </c>
       <c r="R22" t="n">
-        <v>6587896</v>
+        <v>6587651</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133157943</v>
+        <v>133163899</v>
       </c>
       <c r="B23" t="n">
-        <v>79923</v>
+        <v>5178</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>102204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478785</v>
+        <v>478815</v>
       </c>
       <c r="R23" t="n">
-        <v>6587651</v>
+        <v>6587811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,45 +3057,59 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133164424</v>
+        <v>133158095</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478877</v>
+        <v>478787</v>
       </c>
       <c r="R24" t="n">
-        <v>6587894</v>
+        <v>6587663</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,7 +3141,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3137,7 +3151,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Nyligen använd sandbadgrop.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3164,59 +3183,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133158095</v>
+        <v>133164424</v>
       </c>
       <c r="B25" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478787</v>
+        <v>478877</v>
       </c>
       <c r="R25" t="n">
-        <v>6587663</v>
+        <v>6587894</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3248,7 +3253,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3258,12 +3263,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Nyligen använd sandbadgrop.</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -1631,7 +1631,7 @@
         <v>133156072</v>
       </c>
       <c r="B11" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>133163474</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133163939</v>
+        <v>133165025</v>
       </c>
       <c r="B13" t="n">
         <v>57145</v>
@@ -1892,14 +1892,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478815</v>
+        <v>478792</v>
       </c>
       <c r="R13" t="n">
-        <v>6587811</v>
+        <v>6587923</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,7 +1968,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133165025</v>
+        <v>133163939</v>
       </c>
       <c r="B14" t="n">
         <v>57145</v>
@@ -2018,14 +2018,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478792</v>
+        <v>478815</v>
       </c>
       <c r="R14" t="n">
-        <v>6587923</v>
+        <v>6587811</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,10 +2094,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133164621</v>
+        <v>133164100</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478849</v>
+        <v>478836</v>
       </c>
       <c r="R15" t="n">
-        <v>6587928</v>
+        <v>6587889</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133164100</v>
+        <v>133164621</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478836</v>
+        <v>478849</v>
       </c>
       <c r="R16" t="n">
-        <v>6587889</v>
+        <v>6587928</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2311,7 +2311,7 @@
         <v>133162464</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>133163021</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>133163674</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>133163535</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133164017</v>
+        <v>133157943</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>79924</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478847</v>
+        <v>478785</v>
       </c>
       <c r="R21" t="n">
-        <v>6587896</v>
+        <v>6587651</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133157943</v>
+        <v>133164017</v>
       </c>
       <c r="B22" t="n">
-        <v>79923</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478785</v>
+        <v>478847</v>
       </c>
       <c r="R22" t="n">
-        <v>6587651</v>
+        <v>6587896</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,59 +3057,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133158095</v>
+        <v>133164424</v>
       </c>
       <c r="B24" t="n">
-        <v>57145</v>
+        <v>79334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478787</v>
+        <v>478877</v>
       </c>
       <c r="R24" t="n">
-        <v>6587663</v>
+        <v>6587894</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,7 +3127,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3151,12 +3137,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Nyligen använd sandbadgrop.</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3183,45 +3164,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133164424</v>
+        <v>133158095</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478877</v>
+        <v>478787</v>
       </c>
       <c r="R25" t="n">
-        <v>6587894</v>
+        <v>6587663</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,7 +3248,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3263,7 +3258,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Nyligen använd sandbadgrop.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3290,45 +3290,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133158861</v>
+        <v>133159508</v>
       </c>
       <c r="B26" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478760</v>
+        <v>478797</v>
       </c>
       <c r="R26" t="n">
-        <v>6587688</v>
+        <v>6587811</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,7 +3374,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3370,7 +3384,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bohål i tallhögstubbe passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3397,10 +3416,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133164945</v>
+        <v>133158861</v>
       </c>
       <c r="B27" t="n">
-        <v>57145</v>
+        <v>91883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,53 +3427,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478829</v>
+        <v>478760</v>
       </c>
       <c r="R27" t="n">
-        <v>6587835</v>
+        <v>6587688</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3523,7 +3523,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133159244</v>
+        <v>133164945</v>
       </c>
       <c r="B28" t="n">
         <v>57145</v>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478774</v>
+        <v>478829</v>
       </c>
       <c r="R28" t="n">
-        <v>6587757</v>
+        <v>6587835</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,32 +3649,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133159508</v>
+        <v>133159244</v>
       </c>
       <c r="B29" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3687,9 +3687,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3698,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478797</v>
+        <v>478774</v>
       </c>
       <c r="R29" t="n">
-        <v>6587811</v>
+        <v>6587757</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3733,7 +3738,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3743,12 +3748,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bohål i tallhögstubbe passande för pärluggla.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3775,64 +3775,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133165225</v>
+        <v>133163490</v>
       </c>
       <c r="B30" t="n">
-        <v>57145</v>
+        <v>79334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478778</v>
+        <v>478839</v>
       </c>
       <c r="R30" t="n">
-        <v>6587929</v>
+        <v>6587846</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3864,7 +3845,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3874,7 +3855,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3901,32 +3882,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133157237</v>
+        <v>133165225</v>
       </c>
       <c r="B31" t="n">
-        <v>58119</v>
+        <v>57145</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3939,21 +3920,26 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478750</v>
+        <v>478778</v>
       </c>
       <c r="R31" t="n">
-        <v>6587597</v>
+        <v>6587929</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3985,7 +3971,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3995,12 +3981,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4027,10 +4008,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133163490</v>
+        <v>133157237</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>58119</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4038,34 +4019,48 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478839</v>
+        <v>478750</v>
       </c>
       <c r="R32" t="n">
-        <v>6587846</v>
+        <v>6587597</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4097,7 +4092,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4107,7 +4102,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4134,32 +4134,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133163377</v>
+        <v>133157471</v>
       </c>
       <c r="B33" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4172,6 +4172,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4183,10 +4188,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478858</v>
+        <v>478782</v>
       </c>
       <c r="R33" t="n">
-        <v>6587872</v>
+        <v>6587621</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4218,7 +4223,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4228,12 +4233,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Inhack efter hästmyror i innanmurken torrgran.</t>
+          <t>Nyligen använd sandbadgrop med tappat dun.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4260,32 +4265,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133157471</v>
+        <v>133163377</v>
       </c>
       <c r="B34" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4298,11 +4303,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478782</v>
+        <v>478858</v>
       </c>
       <c r="R34" t="n">
-        <v>6587621</v>
+        <v>6587872</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4359,12 +4359,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Nyligen använd sandbadgrop med tappat dun.</t>
+          <t>Inhack efter hästmyror i innanmurken torrgran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133158110</v>
+        <v>133164491</v>
       </c>
       <c r="B35" t="n">
-        <v>91881</v>
+        <v>79334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478783</v>
+        <v>478853</v>
       </c>
       <c r="R35" t="n">
-        <v>6587658</v>
+        <v>6587853</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,32 +4498,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133164491</v>
+        <v>133158110</v>
       </c>
       <c r="B36" t="n">
-        <v>79333</v>
+        <v>91883</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478853</v>
+        <v>478783</v>
       </c>
       <c r="R36" t="n">
-        <v>6587853</v>
+        <v>6587658</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4608,7 +4608,7 @@
         <v>133163174</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>133158199</v>
       </c>
       <c r="B38" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>133156829</v>
       </c>
       <c r="B39" t="n">
-        <v>91291</v>
+        <v>91293</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>133159278</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>133159122</v>
       </c>
       <c r="B41" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,45 +5140,59 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133162758</v>
+        <v>133158375</v>
       </c>
       <c r="B42" t="n">
-        <v>92342</v>
+        <v>58119</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4217</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478859</v>
+        <v>478745</v>
       </c>
       <c r="R42" t="n">
-        <v>6587856</v>
+        <v>6587630</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5210,7 +5224,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5220,7 +5234,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5247,59 +5266,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133158375</v>
+        <v>133162758</v>
       </c>
       <c r="B43" t="n">
-        <v>58119</v>
+        <v>92344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>4217</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478745</v>
+        <v>478859</v>
       </c>
       <c r="R43" t="n">
-        <v>6587630</v>
+        <v>6587856</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5331,7 +5336,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5341,12 +5346,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5884,7 +5884,7 @@
         <v>133329228</v>
       </c>
       <c r="B48" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133157943</v>
+        <v>133163899</v>
       </c>
       <c r="B21" t="n">
-        <v>79924</v>
+        <v>5178</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>102204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478785</v>
+        <v>478815</v>
       </c>
       <c r="R21" t="n">
-        <v>6587651</v>
+        <v>6587811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133164017</v>
+        <v>133157943</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>79924</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478847</v>
+        <v>478785</v>
       </c>
       <c r="R22" t="n">
-        <v>6587896</v>
+        <v>6587651</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133163899</v>
+        <v>133164017</v>
       </c>
       <c r="B23" t="n">
-        <v>5178</v>
+        <v>79334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102204</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478815</v>
+        <v>478847</v>
       </c>
       <c r="R23" t="n">
-        <v>6587811</v>
+        <v>6587896</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133163899</v>
+        <v>133157943</v>
       </c>
       <c r="B21" t="n">
-        <v>5178</v>
+        <v>79924</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102204</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478815</v>
+        <v>478785</v>
       </c>
       <c r="R21" t="n">
-        <v>6587811</v>
+        <v>6587651</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133157943</v>
+        <v>133164017</v>
       </c>
       <c r="B22" t="n">
-        <v>79924</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478785</v>
+        <v>478847</v>
       </c>
       <c r="R22" t="n">
-        <v>6587651</v>
+        <v>6587896</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133164017</v>
+        <v>133163899</v>
       </c>
       <c r="B23" t="n">
-        <v>79334</v>
+        <v>5178</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>102204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478847</v>
+        <v>478815</v>
       </c>
       <c r="R23" t="n">
-        <v>6587896</v>
+        <v>6587811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -1628,45 +1628,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133156072</v>
+        <v>133163474</v>
       </c>
       <c r="B11" t="n">
-        <v>91883</v>
+        <v>79334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478789</v>
+        <v>478842</v>
       </c>
       <c r="R11" t="n">
-        <v>6587344</v>
+        <v>6587847</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,45 +1735,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133163474</v>
+        <v>133156072</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478842</v>
+        <v>478789</v>
       </c>
       <c r="R12" t="n">
-        <v>6587847</v>
+        <v>6587344</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133157943</v>
+        <v>133164017</v>
       </c>
       <c r="B21" t="n">
-        <v>79924</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478785</v>
+        <v>478847</v>
       </c>
       <c r="R21" t="n">
-        <v>6587651</v>
+        <v>6587896</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133164017</v>
+        <v>133163899</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>5178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478847</v>
+        <v>478815</v>
       </c>
       <c r="R22" t="n">
-        <v>6587896</v>
+        <v>6587811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133163899</v>
+        <v>133157943</v>
       </c>
       <c r="B23" t="n">
-        <v>5178</v>
+        <v>79924</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102204</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478815</v>
+        <v>478785</v>
       </c>
       <c r="R23" t="n">
-        <v>6587811</v>
+        <v>6587651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,45 +3057,59 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133164424</v>
+        <v>133158095</v>
       </c>
       <c r="B24" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478877</v>
+        <v>478787</v>
       </c>
       <c r="R24" t="n">
-        <v>6587894</v>
+        <v>6587663</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,7 +3141,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3137,7 +3151,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Nyligen använd sandbadgrop.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3164,59 +3183,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133158095</v>
+        <v>133164424</v>
       </c>
       <c r="B25" t="n">
-        <v>57145</v>
+        <v>79334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478787</v>
+        <v>478877</v>
       </c>
       <c r="R25" t="n">
-        <v>6587663</v>
+        <v>6587894</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3248,7 +3253,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3258,12 +3263,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Nyligen använd sandbadgrop.</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3290,59 +3290,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133159508</v>
+        <v>133158861</v>
       </c>
       <c r="B26" t="n">
-        <v>57955</v>
+        <v>91891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478797</v>
+        <v>478760</v>
       </c>
       <c r="R26" t="n">
-        <v>6587811</v>
+        <v>6587688</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3374,7 +3360,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3384,12 +3370,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Bohål i tallhögstubbe passande för pärluggla.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3416,45 +3397,59 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133158861</v>
+        <v>133159508</v>
       </c>
       <c r="B27" t="n">
-        <v>91883</v>
+        <v>57955</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478760</v>
+        <v>478797</v>
       </c>
       <c r="R27" t="n">
-        <v>6587688</v>
+        <v>6587811</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,7 +3481,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3496,7 +3491,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Bohål i tallhögstubbe passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4134,32 +4134,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133157471</v>
+        <v>133163377</v>
       </c>
       <c r="B33" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4172,11 +4172,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4188,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478782</v>
+        <v>478858</v>
       </c>
       <c r="R33" t="n">
-        <v>6587621</v>
+        <v>6587872</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4223,7 +4218,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4233,12 +4228,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Nyligen använd sandbadgrop med tappat dun.</t>
+          <t>Inhack efter hästmyror i innanmurken torrgran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4265,32 +4260,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133163377</v>
+        <v>133157471</v>
       </c>
       <c r="B34" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4303,6 +4298,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478858</v>
+        <v>478782</v>
       </c>
       <c r="R34" t="n">
-        <v>6587872</v>
+        <v>6587621</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4359,12 +4359,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Inhack efter hästmyror i innanmurken torrgran.</t>
+          <t>Nyligen använd sandbadgrop med tappat dun.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4501,7 +4501,7 @@
         <v>133158110</v>
       </c>
       <c r="B36" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>133158199</v>
       </c>
       <c r="B38" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>133156829</v>
       </c>
       <c r="B39" t="n">
-        <v>91293</v>
+        <v>91301</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5140,59 +5140,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133158375</v>
+        <v>133162758</v>
       </c>
       <c r="B42" t="n">
-        <v>58119</v>
+        <v>92352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>4217</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478745</v>
+        <v>478859</v>
       </c>
       <c r="R42" t="n">
-        <v>6587630</v>
+        <v>6587856</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5224,7 +5210,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5234,12 +5220,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5266,45 +5247,59 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133162758</v>
+        <v>133158375</v>
       </c>
       <c r="B43" t="n">
-        <v>92344</v>
+        <v>58119</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4217</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478859</v>
+        <v>478745</v>
       </c>
       <c r="R43" t="n">
-        <v>6587856</v>
+        <v>6587630</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5336,7 +5331,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5346,7 +5341,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -1628,45 +1628,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133163474</v>
+        <v>133156072</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478842</v>
+        <v>478789</v>
       </c>
       <c r="R11" t="n">
-        <v>6587847</v>
+        <v>6587344</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133156072</v>
+        <v>133165025</v>
       </c>
       <c r="B12" t="n">
-        <v>91891</v>
+        <v>57145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,34 +1746,53 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478789</v>
+        <v>478792</v>
       </c>
       <c r="R12" t="n">
-        <v>6587344</v>
+        <v>6587923</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1861,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133165025</v>
+        <v>133163939</v>
       </c>
       <c r="B13" t="n">
         <v>57145</v>
@@ -1892,14 +1911,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478792</v>
+        <v>478815</v>
       </c>
       <c r="R13" t="n">
-        <v>6587923</v>
+        <v>6587811</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1950,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1960,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,64 +1987,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133163939</v>
+        <v>133163474</v>
       </c>
       <c r="B14" t="n">
-        <v>57145</v>
+        <v>79334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478815</v>
+        <v>478842</v>
       </c>
       <c r="R14" t="n">
-        <v>6587811</v>
+        <v>6587847</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133164017</v>
+        <v>133163899</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>5178</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478847</v>
+        <v>478815</v>
       </c>
       <c r="R21" t="n">
-        <v>6587896</v>
+        <v>6587811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133163899</v>
+        <v>133164017</v>
       </c>
       <c r="B22" t="n">
-        <v>5178</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102204</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478815</v>
+        <v>478847</v>
       </c>
       <c r="R22" t="n">
-        <v>6587811</v>
+        <v>6587896</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133163899</v>
+        <v>133164017</v>
       </c>
       <c r="B21" t="n">
-        <v>5178</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102204</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478815</v>
+        <v>478847</v>
       </c>
       <c r="R21" t="n">
-        <v>6587811</v>
+        <v>6587896</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133164017</v>
+        <v>133163899</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>5178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478847</v>
+        <v>478815</v>
       </c>
       <c r="R22" t="n">
-        <v>6587896</v>
+        <v>6587811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,59 +3057,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133158095</v>
+        <v>133164424</v>
       </c>
       <c r="B24" t="n">
-        <v>57145</v>
+        <v>79334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478787</v>
+        <v>478877</v>
       </c>
       <c r="R24" t="n">
-        <v>6587663</v>
+        <v>6587894</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,7 +3127,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3151,12 +3137,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Nyligen använd sandbadgrop.</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3183,45 +3164,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133164424</v>
+        <v>133158095</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478877</v>
+        <v>478787</v>
       </c>
       <c r="R25" t="n">
-        <v>6587894</v>
+        <v>6587663</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,7 +3248,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3263,7 +3258,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Nyligen använd sandbadgrop.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -1628,45 +1628,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133156072</v>
+        <v>133163474</v>
       </c>
       <c r="B11" t="n">
-        <v>91891</v>
+        <v>79334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478789</v>
+        <v>478842</v>
       </c>
       <c r="R11" t="n">
-        <v>6587344</v>
+        <v>6587847</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133165025</v>
+        <v>133156072</v>
       </c>
       <c r="B12" t="n">
-        <v>57145</v>
+        <v>91891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,53 +1746,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478792</v>
+        <v>478789</v>
       </c>
       <c r="R12" t="n">
-        <v>6587923</v>
+        <v>6587344</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1834,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133163939</v>
+        <v>133165025</v>
       </c>
       <c r="B13" t="n">
         <v>57145</v>
@@ -1911,14 +1892,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478815</v>
+        <v>478792</v>
       </c>
       <c r="R13" t="n">
-        <v>6587811</v>
+        <v>6587923</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1960,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,45 +1968,64 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133163474</v>
+        <v>133163939</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478842</v>
+        <v>478815</v>
       </c>
       <c r="R14" t="n">
-        <v>6587847</v>
+        <v>6587811</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133163899</v>
+        <v>133164017</v>
       </c>
       <c r="B21" t="n">
-        <v>5178</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102204</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478815</v>
+        <v>478847</v>
       </c>
       <c r="R21" t="n">
-        <v>6587811</v>
+        <v>6587896</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133164017</v>
+        <v>133163899</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>5178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478847</v>
+        <v>478815</v>
       </c>
       <c r="R22" t="n">
-        <v>6587896</v>
+        <v>6587811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,45 +3057,59 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133164424</v>
+        <v>133158095</v>
       </c>
       <c r="B24" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478877</v>
+        <v>478787</v>
       </c>
       <c r="R24" t="n">
-        <v>6587894</v>
+        <v>6587663</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,7 +3141,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3137,7 +3151,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Nyligen använd sandbadgrop.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3164,59 +3183,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133158095</v>
+        <v>133164424</v>
       </c>
       <c r="B25" t="n">
-        <v>57145</v>
+        <v>79334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478787</v>
+        <v>478877</v>
       </c>
       <c r="R25" t="n">
-        <v>6587663</v>
+        <v>6587894</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3248,7 +3253,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3258,12 +3263,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Nyligen använd sandbadgrop.</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -1631,7 +1631,7 @@
         <v>133156072</v>
       </c>
       <c r="B11" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,64 +1735,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133165025</v>
+        <v>133163474</v>
       </c>
       <c r="B12" t="n">
-        <v>57145</v>
+        <v>79348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478792</v>
+        <v>478842</v>
       </c>
       <c r="R12" t="n">
-        <v>6587923</v>
+        <v>6587847</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1834,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133163939</v>
+        <v>133165025</v>
       </c>
       <c r="B13" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,14 +1892,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478815</v>
+        <v>478792</v>
       </c>
       <c r="R13" t="n">
-        <v>6587811</v>
+        <v>6587923</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1960,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,45 +1968,64 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133163474</v>
+        <v>133163939</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>57152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478842</v>
+        <v>478815</v>
       </c>
       <c r="R14" t="n">
-        <v>6587847</v>
+        <v>6587811</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,7 +2097,7 @@
         <v>133164100</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>133164621</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>133162464</v>
       </c>
       <c r="B17" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>133163021</v>
       </c>
       <c r="B18" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>133163674</v>
       </c>
       <c r="B19" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>133163535</v>
       </c>
       <c r="B20" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133164017</v>
+        <v>133157943</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>79938</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478847</v>
+        <v>478785</v>
       </c>
       <c r="R21" t="n">
-        <v>6587896</v>
+        <v>6587651</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2846,7 +2846,7 @@
         <v>133163899</v>
       </c>
       <c r="B22" t="n">
-        <v>5178</v>
+        <v>5180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133157943</v>
+        <v>133164017</v>
       </c>
       <c r="B23" t="n">
-        <v>79924</v>
+        <v>79348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478785</v>
+        <v>478847</v>
       </c>
       <c r="R23" t="n">
-        <v>6587651</v>
+        <v>6587896</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,7 +3060,7 @@
         <v>133158095</v>
       </c>
       <c r="B24" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>133164424</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>133158861</v>
       </c>
       <c r="B26" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>133159508</v>
       </c>
       <c r="B27" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>133164945</v>
       </c>
       <c r="B28" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>133159244</v>
       </c>
       <c r="B29" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3775,10 +3775,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133163490</v>
+        <v>133157237</v>
       </c>
       <c r="B30" t="n">
-        <v>79334</v>
+        <v>58126</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,34 +3786,48 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478839</v>
+        <v>478750</v>
       </c>
       <c r="R30" t="n">
-        <v>6587846</v>
+        <v>6587597</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3845,7 +3859,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3855,7 +3869,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3885,7 +3904,7 @@
         <v>133165225</v>
       </c>
       <c r="B31" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4008,10 +4027,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133157237</v>
+        <v>133163490</v>
       </c>
       <c r="B32" t="n">
-        <v>58119</v>
+        <v>79348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4019,48 +4038,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478750</v>
+        <v>478839</v>
       </c>
       <c r="R32" t="n">
-        <v>6587597</v>
+        <v>6587846</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4092,7 +4097,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4102,12 +4107,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4134,32 +4134,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133163377</v>
+        <v>133157471</v>
       </c>
       <c r="B33" t="n">
-        <v>57955</v>
+        <v>57152</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4172,6 +4172,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4183,10 +4188,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478858</v>
+        <v>478782</v>
       </c>
       <c r="R33" t="n">
-        <v>6587872</v>
+        <v>6587621</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4218,7 +4223,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4228,12 +4233,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Inhack efter hästmyror i innanmurken torrgran.</t>
+          <t>Nyligen använd sandbadgrop med tappat dun.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4260,32 +4265,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133157471</v>
+        <v>133163377</v>
       </c>
       <c r="B34" t="n">
-        <v>57145</v>
+        <v>57962</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4298,11 +4303,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478782</v>
+        <v>478858</v>
       </c>
       <c r="R34" t="n">
-        <v>6587621</v>
+        <v>6587872</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4359,12 +4359,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Nyligen använd sandbadgrop med tappat dun.</t>
+          <t>Inhack efter hästmyror i innanmurken torrgran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4394,7 +4394,7 @@
         <v>133164491</v>
       </c>
       <c r="B35" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>133158110</v>
       </c>
       <c r="B36" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>133163174</v>
       </c>
       <c r="B37" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>133158199</v>
       </c>
       <c r="B38" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>133156829</v>
       </c>
       <c r="B39" t="n">
-        <v>91301</v>
+        <v>91320</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>133159278</v>
       </c>
       <c r="B40" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>133159122</v>
       </c>
       <c r="B41" t="n">
-        <v>79953</v>
+        <v>79967</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>133162758</v>
       </c>
       <c r="B42" t="n">
-        <v>92352</v>
+        <v>92343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>133158375</v>
       </c>
       <c r="B43" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>133329066</v>
       </c>
       <c r="B44" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>133328895</v>
       </c>
       <c r="B45" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>133328970</v>
       </c>
       <c r="B46" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>133328830</v>
       </c>
       <c r="B47" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>133329228</v>
       </c>
       <c r="B48" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>133328864</v>
       </c>
       <c r="B49" t="n">
-        <v>57607</v>
+        <v>57614</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -5376,7 +5376,7 @@
         <v>133329066</v>
       </c>
       <c r="B44" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>133328895</v>
       </c>
       <c r="B45" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>133328970</v>
       </c>
       <c r="B46" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>133328830</v>
       </c>
       <c r="B47" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>133329228</v>
       </c>
       <c r="B48" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>133328864</v>
       </c>
       <c r="B49" t="n">
-        <v>57614</v>
+        <v>57624</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131621313</v>
+        <v>133162758</v>
       </c>
       <c r="B2" t="n">
-        <v>79929</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>kroktjärn, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478776</v>
+        <v>478859</v>
       </c>
       <c r="R2" t="n">
-        <v>6587602</v>
+        <v>6587856</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,70 +764,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131621388</v>
+        <v>132318247</v>
       </c>
       <c r="B3" t="n">
-        <v>91847</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kroktjärn, Vrm</t>
+          <t>Granbergsdal, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478746</v>
+        <v>478716</v>
       </c>
       <c r="R3" t="n">
-        <v>6587485</v>
+        <v>6587597</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -844,12 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,58 +870,53 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131621412</v>
+        <v>131621380</v>
       </c>
       <c r="B4" t="n">
-        <v>92303</v>
+        <v>91937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040162</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -919,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478737</v>
+        <v>478764</v>
       </c>
       <c r="R4" t="n">
-        <v>6587466</v>
+        <v>6587422</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -957,16 +964,11 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
@@ -987,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131621380</v>
+        <v>131621388</v>
       </c>
       <c r="B5" t="n">
-        <v>91847</v>
+        <v>91937</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478764</v>
+        <v>478746</v>
       </c>
       <c r="R5" t="n">
-        <v>6587422</v>
+        <v>6587485</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,7 +1093,7 @@
         <v>131621393</v>
       </c>
       <c r="B6" t="n">
-        <v>91847</v>
+        <v>91937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131621297</v>
+        <v>133156072</v>
       </c>
       <c r="B7" t="n">
-        <v>57136</v>
+        <v>91937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,61 +1202,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kroktjärn, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478775</v>
+        <v>478789</v>
       </c>
       <c r="R7" t="n">
-        <v>6587647</v>
+        <v>6587344</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,12 +1256,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,61 +1286,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132318246</v>
+        <v>133158110</v>
       </c>
       <c r="B8" t="n">
-        <v>79951</v>
+        <v>91937</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Granbergsdal, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478766</v>
+        <v>478783</v>
       </c>
       <c r="R8" t="n">
-        <v>6587600</v>
+        <v>6587658</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,17 +1363,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,22 +1393,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132318248</v>
+        <v>133158199</v>
       </c>
       <c r="B9" t="n">
-        <v>97993</v>
+        <v>91937</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,38 +1416,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Granbergsdal, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478726</v>
+        <v>478782</v>
       </c>
       <c r="R9" t="n">
-        <v>6587683</v>
+        <v>6587657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,17 +1470,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,22 +1500,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132318247</v>
+        <v>133158861</v>
       </c>
       <c r="B10" t="n">
-        <v>93204</v>
+        <v>91937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1533,38 +1523,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granbergsdal, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478716</v>
+        <v>478760</v>
       </c>
       <c r="R10" t="n">
-        <v>6587597</v>
+        <v>6587688</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,17 +1577,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,22 +1607,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133156072</v>
+        <v>133164373</v>
       </c>
       <c r="B11" t="n">
-        <v>91910</v>
+        <v>91937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,14 +1650,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478789</v>
+        <v>478897</v>
       </c>
       <c r="R11" t="n">
-        <v>6587344</v>
+        <v>6587904</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1689,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1699,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,45 +1726,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133163474</v>
+        <v>133156829</v>
       </c>
       <c r="B12" t="n">
-        <v>79348</v>
+        <v>91347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478842</v>
+        <v>478727</v>
       </c>
       <c r="R12" t="n">
-        <v>6587847</v>
+        <v>6587538</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1796,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1806,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,32 +1833,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133165025</v>
+        <v>132318245</v>
       </c>
       <c r="B13" t="n">
-        <v>57152</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1875,31 +1866,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+          <t>Granbergsdal, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478792</v>
+        <v>478854</v>
       </c>
       <c r="R13" t="n">
-        <v>6587923</v>
+        <v>6587829</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,22 +1902,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,76 +1927,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133163939</v>
+        <v>133159278</v>
       </c>
       <c r="B14" t="n">
-        <v>57152</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478815</v>
+        <v>478797</v>
       </c>
       <c r="R14" t="n">
-        <v>6587811</v>
+        <v>6587770</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2009,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2067,7 +2019,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,14 +2046,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133164100</v>
+        <v>133162464</v>
       </c>
       <c r="B15" t="n">
-        <v>79348</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2129,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478836</v>
+        <v>478846</v>
       </c>
       <c r="R15" t="n">
-        <v>6587889</v>
+        <v>6587867</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2116,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2126,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,14 +2153,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133164621</v>
+        <v>133163021</v>
       </c>
       <c r="B16" t="n">
-        <v>79348</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2236,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478849</v>
+        <v>478867</v>
       </c>
       <c r="R16" t="n">
-        <v>6587928</v>
+        <v>6587867</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2223,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2281,7 +2233,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,14 +2260,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133162464</v>
+        <v>133163174</v>
       </c>
       <c r="B17" t="n">
-        <v>79348</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2343,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478846</v>
+        <v>478886</v>
       </c>
       <c r="R17" t="n">
-        <v>6587867</v>
+        <v>6587878</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,7 +2330,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2388,7 +2340,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,14 +2367,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133163021</v>
+        <v>133163474</v>
       </c>
       <c r="B18" t="n">
-        <v>79348</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2450,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478867</v>
+        <v>478842</v>
       </c>
       <c r="R18" t="n">
-        <v>6587867</v>
+        <v>6587847</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,7 +2437,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2495,7 +2447,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,14 +2474,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133163674</v>
+        <v>133163490</v>
       </c>
       <c r="B19" t="n">
-        <v>79348</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2557,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478789</v>
+        <v>478839</v>
       </c>
       <c r="R19" t="n">
-        <v>6587780</v>
+        <v>6587846</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2544,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2602,7 +2554,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,11 +2584,11 @@
         <v>133163535</v>
       </c>
       <c r="B20" t="n">
-        <v>79348</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2736,32 +2688,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133157943</v>
+        <v>133163612</v>
       </c>
       <c r="B21" t="n">
-        <v>79938</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2771,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478785</v>
+        <v>478810</v>
       </c>
       <c r="R21" t="n">
-        <v>6587651</v>
+        <v>6587773</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2758,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2768,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,32 +2795,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133163899</v>
+        <v>133163674</v>
       </c>
       <c r="B22" t="n">
-        <v>5180</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102204</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2878,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478815</v>
+        <v>478789</v>
       </c>
       <c r="R22" t="n">
-        <v>6587811</v>
+        <v>6587780</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2865,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2875,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2953,11 +2905,11 @@
         <v>133164017</v>
       </c>
       <c r="B23" t="n">
-        <v>79348</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3057,59 +3009,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133158095</v>
+        <v>133164100</v>
       </c>
       <c r="B24" t="n">
-        <v>57152</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478787</v>
+        <v>478836</v>
       </c>
       <c r="R24" t="n">
-        <v>6587663</v>
+        <v>6587889</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,7 +3079,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3151,12 +3089,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Nyligen använd sandbadgrop.</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3183,14 +3116,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133164424</v>
+        <v>133164261</v>
       </c>
       <c r="B25" t="n">
-        <v>79348</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3218,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478877</v>
+        <v>478862</v>
       </c>
       <c r="R25" t="n">
-        <v>6587894</v>
+        <v>6587941</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,7 +3186,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3263,7 +3196,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3290,32 +3223,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133158861</v>
+        <v>133164357</v>
       </c>
       <c r="B26" t="n">
-        <v>91910</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478760</v>
+        <v>478884</v>
       </c>
       <c r="R26" t="n">
-        <v>6587688</v>
+        <v>6587908</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,7 +3293,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3370,7 +3303,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3397,59 +3330,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133159508</v>
+        <v>133164424</v>
       </c>
       <c r="B27" t="n">
-        <v>57962</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478797</v>
+        <v>478877</v>
       </c>
       <c r="R27" t="n">
-        <v>6587811</v>
+        <v>6587894</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3481,7 +3400,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3491,12 +3410,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Bohål i tallhögstubbe passande för pärluggla.</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3523,64 +3437,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133164945</v>
+        <v>133164491</v>
       </c>
       <c r="B28" t="n">
-        <v>57152</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478829</v>
+        <v>478853</v>
       </c>
       <c r="R28" t="n">
-        <v>6587835</v>
+        <v>6587853</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3612,7 +3507,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3622,7 +3517,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,64 +3544,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133159244</v>
+        <v>133164621</v>
       </c>
       <c r="B29" t="n">
-        <v>57152</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478774</v>
+        <v>478849</v>
       </c>
       <c r="R29" t="n">
-        <v>6587757</v>
+        <v>6587928</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3738,7 +3614,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3748,7 +3624,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3775,59 +3651,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133157237</v>
+        <v>133329228</v>
       </c>
       <c r="B30" t="n">
-        <v>58126</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478750</v>
+        <v>478838</v>
       </c>
       <c r="R30" t="n">
-        <v>6587597</v>
+        <v>6587835</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3854,27 +3716,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3901,67 +3758,51 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133165225</v>
+        <v>131621313</v>
       </c>
       <c r="B31" t="n">
-        <v>57152</v>
+        <v>79992</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+          <t>kroktjärn, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478778</v>
+        <v>478776</v>
       </c>
       <c r="R31" t="n">
-        <v>6587929</v>
+        <v>6587602</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3985,22 +3826,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4009,28 +3840,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133163490</v>
+        <v>132318246</v>
       </c>
       <c r="B32" t="n">
-        <v>79348</v>
+        <v>79992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4038,34 +3870,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Granbergsdal, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478839</v>
+        <v>478766</v>
       </c>
       <c r="R32" t="n">
-        <v>6587846</v>
+        <v>6587600</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4092,22 +3928,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4122,76 +3953,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133157471</v>
+        <v>133159122</v>
       </c>
       <c r="B33" t="n">
-        <v>57152</v>
+        <v>79992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478782</v>
+        <v>478736</v>
       </c>
       <c r="R33" t="n">
-        <v>6587621</v>
+        <v>6587758</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4223,7 +4035,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4233,12 +4045,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Nyligen använd sandbadgrop med tappat dun.</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4265,14 +4072,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133163377</v>
+        <v>133159508</v>
       </c>
       <c r="B34" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4305,7 +4112,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4314,10 +4121,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478858</v>
+        <v>478797</v>
       </c>
       <c r="R34" t="n">
-        <v>6587872</v>
+        <v>6587811</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,7 +4156,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4359,12 +4166,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Inhack efter hästmyror i innanmurken torrgran.</t>
+          <t>Bohål i tallhögstubbe passande för pärluggla.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,45 +4198,59 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133164491</v>
+        <v>133163377</v>
       </c>
       <c r="B35" t="n">
-        <v>79348</v>
+        <v>57972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478853</v>
+        <v>478858</v>
       </c>
       <c r="R35" t="n">
-        <v>6587853</v>
+        <v>6587872</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4461,7 +4282,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,7 +4292,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Inhack efter hästmyror i innanmurken torrgran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,10 +4324,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133158110</v>
+        <v>133328864</v>
       </c>
       <c r="B36" t="n">
-        <v>91910</v>
+        <v>57624</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4509,37 +4335,51 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>100063</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>sträckande NO</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478783</v>
+        <v>478751</v>
       </c>
       <c r="R36" t="n">
-        <v>6587658</v>
+        <v>6587688</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4563,22 +4403,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>05:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>05:23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4605,45 +4445,59 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133163174</v>
+        <v>133329285</v>
       </c>
       <c r="B37" t="n">
-        <v>79348</v>
+        <v>57624</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100063</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478886</v>
+        <v>478710</v>
       </c>
       <c r="R37" t="n">
-        <v>6587878</v>
+        <v>6587484</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4670,22 +4524,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4712,10 +4566,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133158199</v>
+        <v>131621297</v>
       </c>
       <c r="B38" t="n">
-        <v>91910</v>
+        <v>57162</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4723,37 +4577,61 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Kroktjärn, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478782</v>
+        <v>478775</v>
       </c>
       <c r="R38" t="n">
-        <v>6587657</v>
+        <v>6587647</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4777,22 +4655,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4807,22 +4675,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133156829</v>
+        <v>133157471</v>
       </c>
       <c r="B39" t="n">
-        <v>91320</v>
+        <v>57162</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4830,34 +4698,53 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5685</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478727</v>
+        <v>478782</v>
       </c>
       <c r="R39" t="n">
-        <v>6587538</v>
+        <v>6587621</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4889,7 +4776,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4899,7 +4786,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Nyligen använd sandbadgrop med tappat dun.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4926,45 +4818,59 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133159278</v>
+        <v>133158095</v>
       </c>
       <c r="B40" t="n">
-        <v>79348</v>
+        <v>57162</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478797</v>
+        <v>478787</v>
       </c>
       <c r="R40" t="n">
-        <v>6587770</v>
+        <v>6587663</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4996,7 +4902,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5006,7 +4912,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Nyligen använd sandbadgrop.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5033,45 +4944,64 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133159122</v>
+        <v>133159244</v>
       </c>
       <c r="B41" t="n">
-        <v>79967</v>
+        <v>57162</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478736</v>
+        <v>478774</v>
       </c>
       <c r="R41" t="n">
-        <v>6587758</v>
+        <v>6587757</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5103,7 +5033,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5113,7 +5043,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5140,10 +5070,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133162758</v>
+        <v>133163767</v>
       </c>
       <c r="B42" t="n">
-        <v>92343</v>
+        <v>57162</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5151,34 +5081,53 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4217</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478859</v>
+        <v>478790</v>
       </c>
       <c r="R42" t="n">
-        <v>6587856</v>
+        <v>6587739</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5210,7 +5159,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5220,7 +5169,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5247,32 +5196,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133158375</v>
+        <v>133163939</v>
       </c>
       <c r="B43" t="n">
-        <v>58126</v>
+        <v>57162</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5285,9 +5234,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5296,10 +5250,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478745</v>
+        <v>478815</v>
       </c>
       <c r="R43" t="n">
-        <v>6587630</v>
+        <v>6587811</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5331,7 +5285,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5341,12 +5295,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5373,32 +5322,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133329066</v>
+        <v>133164945</v>
       </c>
       <c r="B44" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5411,23 +5360,26 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478832</v>
+        <v>478829</v>
       </c>
       <c r="R44" t="n">
-        <v>6587922</v>
+        <v>6587835</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5454,27 +5406,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>06:13</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>06:13</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spel/sång. Filmsnutt finns sparad.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5501,32 +5448,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133328895</v>
+        <v>133165025</v>
       </c>
       <c r="B45" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5539,9 +5486,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5550,10 +5502,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478749</v>
+        <v>478792</v>
       </c>
       <c r="R45" t="n">
-        <v>6587791</v>
+        <v>6587923</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5580,27 +5532,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>05:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>05:33</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5627,32 +5574,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133328970</v>
+        <v>133165225</v>
       </c>
       <c r="B46" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5665,23 +5612,26 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478780</v>
+        <v>478778</v>
       </c>
       <c r="R46" t="n">
-        <v>6587952</v>
+        <v>6587929</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5708,27 +5658,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>05:59</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Filmsnutt finns sparad.</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5755,10 +5700,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133328830</v>
+        <v>133163899</v>
       </c>
       <c r="B47" t="n">
-        <v>58136</v>
+        <v>5180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5766,48 +5711,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>102204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478735</v>
+        <v>478815</v>
       </c>
       <c r="R47" t="n">
-        <v>6587531</v>
+        <v>6587811</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5834,27 +5765,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>05:18</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>05:18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Spel/sång</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5881,10 +5807,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133329228</v>
+        <v>133157237</v>
       </c>
       <c r="B48" t="n">
-        <v>79358</v>
+        <v>58136</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5892,34 +5818,48 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478838</v>
+        <v>478750</v>
       </c>
       <c r="R48" t="n">
-        <v>6587835</v>
+        <v>6587597</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5946,22 +5886,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5988,10 +5933,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133328864</v>
+        <v>133158375</v>
       </c>
       <c r="B49" t="n">
-        <v>57624</v>
+        <v>58136</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5999,21 +5944,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100063</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6028,7 +5973,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>sträckande NO</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6037,13 +5982,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478751</v>
+        <v>478745</v>
       </c>
       <c r="R49" t="n">
-        <v>6587688</v>
+        <v>6587630</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6067,22 +6012,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>05:23</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>05:23</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6106,6 +6056,965 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>133328830</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>478735</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6587531</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>05:18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>05:18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>133328895</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>478749</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6587791</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>05:33</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>05:33</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>133328970</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>478780</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6587952</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Filmsnutt finns sparad.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>133329066</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>478832</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6587922</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>06:13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>06:13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Spel/sång. Filmsnutt finns sparad.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>133329180</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>478867</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6587835</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Spel/sång. Filmsnutt finns sparad.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132318248</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Granbergsdal, Vrm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>478726</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6587683</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133157943</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>478785</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6587651</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>131621412</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92365</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kroktjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>478737</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6587466</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133162758</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318247</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131621380</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131621388</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131621393</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133156072</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133158110</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133158199</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133158861</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1723,6 +1773,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133164373</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1830,6 +1885,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133156829</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1936,6 +1996,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318245</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2043,6 +2108,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133159278</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2150,6 +2220,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133162464</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2257,6 +2332,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163021</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2364,6 +2444,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163174</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2471,6 +2556,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163474</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2578,6 +2668,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163490</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2685,6 +2780,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163535</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163612</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2899,6 +3004,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163674</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3006,6 +3116,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133164017</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3113,6 +3228,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133164100</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3220,6 +3340,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133164261</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3327,6 +3452,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133164357</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3434,6 +3564,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133164424</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3541,6 +3676,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133164491</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3648,6 +3788,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133164621</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3755,6 +3900,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133329228</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3856,6 +4006,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131621313</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3962,6 +4117,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318246</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4069,6 +4229,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133159122</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4195,6 +4360,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133159508</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4321,6 +4491,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163377</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4442,6 +4617,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133328864</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4563,6 +4743,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133329285</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4684,6 +4869,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131621297</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4815,6 +5005,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133157471</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4941,6 +5136,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133158095</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5067,6 +5267,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133159244</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5193,6 +5398,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163767</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5319,6 +5529,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163939</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5445,6 +5660,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133164945</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5571,6 +5791,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133165025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5697,6 +5922,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133165225</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5804,6 +6034,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163899</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5930,6 +6165,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133157237</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6056,6 +6296,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133158375</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6182,6 +6427,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133328830</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6308,6 +6558,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133328895</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6436,6 +6691,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133328970</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6564,6 +6824,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133329066</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6692,6 +6957,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133329180</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6798,6 +7068,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318248</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6905,6 +7180,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133157943</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7015,8 +7295,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131621412</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ57"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6042,32 +6042,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133157237</v>
+        <v>136269756</v>
       </c>
       <c r="B48" t="n">
-        <v>58136</v>
+        <v>57161</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478750</v>
+        <v>478718</v>
       </c>
       <c r="R48" t="n">
-        <v>6587597</v>
+        <v>6587507</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6131,17 +6131,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
           <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6167,13 +6162,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133157237</t>
+          <t>https://artportalen.se/Sighting/136269756</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133158375</v>
+        <v>133157237</v>
       </c>
       <c r="B49" t="n">
         <v>58136</v>
@@ -6218,14 +6213,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478745</v>
+        <v>478750</v>
       </c>
       <c r="R49" t="n">
-        <v>6587630</v>
+        <v>6587597</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6257,7 +6252,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6267,7 +6262,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6298,13 +6293,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133158375</t>
+          <t>https://artportalen.se/Sighting/133157237</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133328830</v>
+        <v>133158375</v>
       </c>
       <c r="B50" t="n">
         <v>58136</v>
@@ -6349,14 +6344,14 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478735</v>
+        <v>478745</v>
       </c>
       <c r="R50" t="n">
-        <v>6587531</v>
+        <v>6587630</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6383,27 +6378,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>05:18</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>05:18</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Spel/sång</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6429,13 +6424,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133328830</t>
+          <t>https://artportalen.se/Sighting/133158375</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133328895</v>
+        <v>133328830</v>
       </c>
       <c r="B51" t="n">
         <v>58136</v>
@@ -6480,14 +6475,14 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478749</v>
+        <v>478735</v>
       </c>
       <c r="R51" t="n">
-        <v>6587791</v>
+        <v>6587531</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6519,7 +6514,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>05:33</t>
+          <t>05:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6529,12 +6524,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>05:33</t>
+          <t>05:18</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Spel/sång.</t>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6560,13 +6555,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133328895</t>
+          <t>https://artportalen.se/Sighting/133328830</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133328970</v>
+        <v>133328895</v>
       </c>
       <c r="B52" t="n">
         <v>58136</v>
@@ -6604,23 +6599,21 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478780</v>
+        <v>478749</v>
       </c>
       <c r="R52" t="n">
-        <v>6587952</v>
+        <v>6587791</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6652,7 +6645,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>05:33</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6662,12 +6655,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>05:33</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Filmsnutt finns sparad.</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6693,13 +6686,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133328970</t>
+          <t>https://artportalen.se/Sighting/133328895</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133329066</v>
+        <v>133328970</v>
       </c>
       <c r="B53" t="n">
         <v>58136</v>
@@ -6740,20 +6733,20 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Stora Kroktjärnen, Granbergsdal, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478832</v>
+        <v>478780</v>
       </c>
       <c r="R53" t="n">
-        <v>6587922</v>
+        <v>6587952</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6785,7 +6778,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>06:13</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6795,12 +6788,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>06:13</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Spel/sång. Filmsnutt finns sparad.</t>
+          <t>Filmsnutt finns sparad.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6826,13 +6819,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133329066</t>
+          <t>https://artportalen.se/Sighting/133328970</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133329180</v>
+        <v>133329066</v>
       </c>
       <c r="B54" t="n">
         <v>58136</v>
@@ -6883,10 +6876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478867</v>
+        <v>478832</v>
       </c>
       <c r="R54" t="n">
-        <v>6587835</v>
+        <v>6587922</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6918,7 +6911,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6928,7 +6921,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:13</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6959,38 +6952,38 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133329180</t>
+          <t>https://artportalen.se/Sighting/133329066</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132318248</v>
+        <v>133329180</v>
       </c>
       <c r="B55" t="n">
-        <v>98063</v>
+        <v>58136</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6998,16 +6991,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Granbergsdal, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478726</v>
+        <v>478867</v>
       </c>
       <c r="R55" t="n">
-        <v>6587683</v>
+        <v>6587835</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7034,17 +7039,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>06:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>06:21</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Spel/sång. Filmsnutt finns sparad.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7059,62 +7074,66 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132318248</t>
+          <t>https://artportalen.se/Sighting/133329180</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133157943</v>
+        <v>132318248</v>
       </c>
       <c r="B56" t="n">
-        <v>79963</v>
+        <v>98063</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>221946</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
+          <t>Granbergsdal, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478785</v>
+        <v>478726</v>
       </c>
       <c r="R56" t="n">
-        <v>6587651</v>
+        <v>6587683</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7141,22 +7160,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7171,27 +7185,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133157943</t>
+          <t>https://artportalen.se/Sighting/132318248</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131621412</v>
+        <v>133157943</v>
       </c>
       <c r="B57" t="n">
-        <v>92365</v>
+        <v>79963</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7199,44 +7213,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6040162</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kroktjärn, Vrm</t>
+          <t>Stora Svarttjärnen, Stora Svarttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478737</v>
+        <v>478785</v>
       </c>
       <c r="R57" t="n">
-        <v>6587466</v>
+        <v>6587651</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7260,42 +7267,161 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133157943</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>131621412</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92365</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kroktjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>478737</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6587466</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131621412</t>
         </is>
@@ -7359,6 +7485,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -6045,7 +6045,7 @@
         <v>136269756</v>
       </c>
       <c r="B48" t="n">
-        <v>57161</v>
+        <v>57165</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -6045,7 +6045,7 @@
         <v>136269756</v>
       </c>
       <c r="B48" t="n">
-        <v>57165</v>
+        <v>57166</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -6045,7 +6045,7 @@
         <v>136269756</v>
       </c>
       <c r="B48" t="n">
-        <v>57166</v>
+        <v>57171</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -6045,7 +6045,7 @@
         <v>136269756</v>
       </c>
       <c r="B48" t="n">
-        <v>57171</v>
+        <v>57184</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
